--- a/assets/docs/empleado/importar/empleado.xlsx
+++ b/assets/docs/empleado/importar/empleado.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\cnomina\assets\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\cnomina\assets\docs\empleado\importar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD0F8911-0695-4E8C-BE8D-6C306DEA9E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C216E40-ADFC-487B-AEA7-63EA0AEEDFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{65C88286-55CE-464B-A52D-D9951CA36E83}"/>
+    <workbookView xWindow="-108" yWindow="252" windowWidth="23256" windowHeight="11952" xr2:uid="{65C88286-55CE-464B-A52D-D9951CA36E83}"/>
   </bookViews>
   <sheets>
     <sheet name="Empleados" sheetId="1" r:id="rId1"/>
+    <sheet name="PERIODO" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t># EMPLEADO</t>
   </si>
@@ -58,9 +59,6 @@
     <t>RFC</t>
   </si>
   <si>
-    <t>TIPO DE TRABAJADOR</t>
-  </si>
-  <si>
     <t>CUENTA BANCARIA</t>
   </si>
   <si>
@@ -85,9 +83,6 @@
     <t>XXXXXXXXXXXXX</t>
   </si>
   <si>
-    <t>BASE</t>
-  </si>
-  <si>
     <t>CATORCENAL</t>
   </si>
   <si>
@@ -95,6 +90,9 @@
   </si>
   <si>
     <t>01/01/2022</t>
+  </si>
+  <si>
+    <t>MENSUAL</t>
   </si>
 </sst>
 </file>
@@ -471,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F527379-0796-45E5-B8DA-938739265192}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" style="4" bestFit="1" customWidth="1"/>
@@ -482,14 +480,13 @@
     <col min="6" max="6" width="19" style="4" customWidth="1"/>
     <col min="7" max="7" width="16.44140625" style="3" customWidth="1"/>
     <col min="8" max="8" width="19.77734375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.5546875" style="3"/>
+    <col min="9" max="9" width="22.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.5546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -523,46 +520,81 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" s="3">
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{BD4729F3-885A-4214-ACD3-4633D34E9898}">
+      <formula1>18</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576" xr:uid="{B9F8F41A-D911-45CB-86D2-FC20F5E10325}">
+      <formula1>10</formula1>
+      <formula2>13</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DC78020-8D78-4E2A-A9A4-0D9C3554C8E5}">
+          <x14:formula1>
+            <xm:f>PERIODO!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>K1:K1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2CBCD3D-3D4E-4DD0-8CA2-DB3FD83617D3}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>19</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/assets/docs/empleado/importar/empleado.xlsx
+++ b/assets/docs/empleado/importar/empleado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\cnomina\assets\docs\empleado\importar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C216E40-ADFC-487B-AEA7-63EA0AEEDFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62D694C-2042-492F-958F-95F29F36B840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="252" windowWidth="23256" windowHeight="11952" xr2:uid="{65C88286-55CE-464B-A52D-D9951CA36E83}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{65C88286-55CE-464B-A52D-D9951CA36E83}"/>
   </bookViews>
   <sheets>
     <sheet name="Empleados" sheetId="1" r:id="rId1"/>
@@ -83,9 +83,6 @@
     <t>XXXXXXXXXXXXX</t>
   </si>
   <si>
-    <t>CATORCENAL</t>
-  </si>
-  <si>
     <t>(OPCIONAL)</t>
   </si>
   <si>
@@ -93,6 +90,9 @@
   </si>
   <si>
     <t>MENSUAL</t>
+  </si>
+  <si>
+    <t>QUINCENAL</t>
   </si>
 </sst>
 </file>
@@ -538,7 +538,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>14</v>
@@ -547,13 +547,13 @@
         <v>15</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -589,12 +589,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
